--- a/translators/xlsx/tests/sample_table.xlsx
+++ b/translators/xlsx/tests/sample_table.xlsx
@@ -42,11 +42,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabella1" displayName="Tabella1" ref="A1:B4" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabella1" displayName="Tabella1" ref="A1:B5" totalsRowCount="1">
   <autoFilter ref="A1:B4"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Codice"/>
-    <tableColumn id="2" name="Descrizione"/>
+    <tableColumn id="2" name="Descrizione" totalsRowFunction="count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -103,6 +103,18 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Totale</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
